--- a/budget_50_30_20.xlsx
+++ b/budget_50_30_20.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
   <si>
     <t xml:space="preserve">Simule Épargne</t>
   </si>
@@ -62,30 +62,57 @@
     <t xml:space="preserve">50% — BESOINS ESSENTIELS</t>
   </si>
   <si>
+    <t xml:space="preserve">✏️ Modifiez les libellés selon votre situation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Loyer / crédit immobilier</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : loyer, remboursement crédit immobilier</t>
+  </si>
+  <si>
     <t xml:space="preserve">Charges &amp; énergie</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : électricité, gaz, eau, internet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alimentation (courses)</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : supermarché, marché, livraisons</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transport</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : métro / bus, essence, assurance voiture</t>
+  </si>
+  <si>
     <t xml:space="preserve">Assurances</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : mutuelle, habitation, prévoyance</t>
+  </si>
+  <si>
     <t xml:space="preserve">Abonnements essentiels</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : téléphone mobile, abonnement pro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santé</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : médecin, pharmacie, lunettes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Garde / scolarité</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : crèche, cantine, cours particuliers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dépensé</t>
   </si>
   <si>
@@ -95,42 +122,81 @@
     <t xml:space="preserve">Restaurants &amp; sorties</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : restaurants, bars, cafés</t>
+  </si>
+  <si>
     <t xml:space="preserve">Voyages &amp; loisirs</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : vacances, week-ends, activités</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shopping &amp; vêtements</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : vêtements, chaussures, accessoires</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sport &amp; bien-être</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : salle de sport, yoga, piscine</t>
+  </si>
+  <si>
     <t xml:space="preserve">Streaming &amp; abonnements loisirs</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : Netflix, Spotify, Disney+, jeux</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cadeaux &amp; occasions</t>
   </si>
   <si>
+    <t xml:space="preserve">ex : anniversaires, fêtes, cadeaux</t>
+  </si>
+  <si>
     <t xml:space="preserve">20% — ÉPARGNE &amp; INVESTISSEMENT</t>
   </si>
   <si>
-    <t xml:space="preserve">PEA (ETF World)</t>
+    <t xml:space="preserve">✏️ Livret A en 1er (sécurité), puis PEA, puis assurance-vie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livret A / LDDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">priorité 1 — filet de sécurité, 3 mois de dépenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">priorité 2 — ouvrir tôt, même avec 10€</t>
   </si>
   <si>
     <t xml:space="preserve">Assurance-vie</t>
   </si>
   <si>
-    <t xml:space="preserve">Livret A / LDDS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO (actions / ETF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crypto (BTC / ETH)</t>
+    <t xml:space="preserve">priorité 3 — après le PEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTO — Compte-titres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">priorité 4 — après PEA et assurance-vie</t>
   </si>
   <si>
     <t xml:space="preserve">Épargne de précaution</t>
   </si>
   <si>
+    <t xml:space="preserve">liquidités disponibles rapidement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Épargne de précaution complémentaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complément si besoin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investi</t>
   </si>
   <si>
@@ -167,13 +233,13 @@
     <t xml:space="preserve">20% — Épargne</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce qui construit ta liberté financière : PEA, AV, CTO, crypto. Priorité PEA jusqu'au plafond, puis AV en UC, puis CTO.</t>
+    <t xml:space="preserve">Ce qui construit ta liberté financière : Livret A, PEA, assurance-vie, CTO. Ordre : Livret A d'abord (filet de sécurité), puis PEA, puis assurance-vie, puis CTO.</t>
   </si>
   <si>
     <t xml:space="preserve">Conseil simulepargne.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Si ton taux d'épargne dépasse 20%, c'est un signal fort. Redirige l'excédent vers ton PEA ou des versements ponctuels sur ton AV Linxea.</t>
+    <t xml:space="preserve">Si ton taux d'épargne dépasse 20%, c'est un signal fort. Redirige l'excédent vers ton PEA en priorité, puis ton assurance-vie.</t>
   </si>
 </sst>
 </file>
@@ -186,7 +252,7 @@
     <numFmt numFmtId="166" formatCode="&quot;Écart : &quot;#,##0&quot; €&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +334,22 @@
       <sz val="10"/>
       <color rgb="FF7A5C1E"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FFB8975A"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF9A9082"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -421,7 +503,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -494,8 +576,12 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -546,43 +632,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -612,7 +698,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF1A5C52"/>
       <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FFB8975A"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF5F0E8"/>
@@ -641,10 +727,10 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFC9A84C"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5F5E5A"/>
-      <rgbColor rgb="FFC9A84C"/>
+      <rgbColor rgb="FF9A9082"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF0D1B2A"/>
@@ -842,8 +928,8 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="3"/>
   </cols>
   <sheetData>
@@ -992,247 +1078,305 @@
         <v>12</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="D17" s="18" t="s">
+        <v>13</v>
+      </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="18"/>
+      <c r="D18" s="19" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="18"/>
+      <c r="D19" s="19" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="18"/>
+      <c r="D20" s="19" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="18"/>
+      <c r="D21" s="19" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="18"/>
+      <c r="D22" s="19" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="18"/>
+      <c r="D23" s="19" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="18"/>
+      <c r="D24" s="19" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="18"/>
+      <c r="D25" s="19" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="20" t="n">
+      <c r="B26" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="21" t="n">
         <f aca="false">SUM(C18:C25)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="22" t="n">
         <f aca="false">C13-C26</f>
         <v>0</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
     </row>
     <row r="27" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="D28" s="18" t="s">
+        <v>13</v>
+      </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="D34" s="19" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="24" t="n">
+      <c r="B35" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="25" t="n">
         <f aca="false">SUM(C29:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="26" t="n">
         <f aca="false">C14-C35</f>
         <v>0</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
     </row>
     <row r="36" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+      <c r="D37" s="18" t="s">
+        <v>45</v>
+      </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="6" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="6" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="D43" s="19" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="28" t="n">
+      <c r="B44" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="29" t="n">
         <f aca="false">SUM(C38:C43)</f>
         <v>0</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="30" t="n">
         <f aca="false">C15-C44</f>
         <v>0</v>
       </c>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
     </row>
     <row r="45" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -1240,10 +1384,10 @@
       <c r="F46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C47" s="32" t="n">
+      <c r="B47" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="33" t="n">
         <f aca="false">C10-C26-C35-C44</f>
         <v>0</v>
       </c>
@@ -1253,19 +1397,19 @@
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="49" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C49" s="34" t="n">
+      <c r="B49" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="35" t="n">
         <f aca="false">IFERROR(C44/C10,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="34" t="n">
+      <c r="B50" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="35" t="n">
         <f aca="false">IFERROR((C26+C35)/C10,0)</f>
         <v>0</v>
       </c>
@@ -1335,8 +1479,8 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
-      <c r="B2" s="35" t="s">
-        <v>41</v>
+      <c r="B2" s="36" t="s">
+        <v>63</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1347,7 +1491,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1365,60 +1509,60 @@
       <c r="G4" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="36" t="s">
-        <v>43</v>
+      <c r="B6" s="37" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="B7" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="38" t="s">
-        <v>45</v>
+      <c r="B9" s="39" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
+      <c r="B10" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="39" t="s">
-        <v>47</v>
+      <c r="B12" s="40" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
+      <c r="B13" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="40" t="s">
-        <v>49</v>
+      <c r="B15" s="41" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
+      <c r="B16" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="4">
